--- a/backend/demo_ordenes_trabajo_v21.xlsx
+++ b/backend/demo_ordenes_trabajo_v21.xlsx
@@ -694,22 +694,22 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-24 11:22:01</t>
+          <t>2026-09-26 05:02:54</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-24 12:22:01</t>
+          <t>2026-09-26 06:02:54</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 12:52:01</t>
+          <t>2026-09-26 06:32:54</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:22:01</t>
+          <t>2026-09-26 08:02:54</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:22:01</t>
+          <t>2026-09-28 08:02:54</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-26 15:22:01</t>
+          <t>2026-09-28 09:02:54</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 15:52:01</t>
+          <t>2026-09-28 09:32:54</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-09-26 17:22:01</t>
+          <t>2026-09-28 11:02:54</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -958,18 +958,18 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-27 21:22:01</t>
+          <t>2026-09-29 15:02:54</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-27 21:52:01</t>
+          <t>2026-09-29 15:32:54</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-09-27 21:52:01</t>
+          <t>2026-09-29 15:32:54</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -1077,22 +1077,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-27 22:22:01</t>
+          <t>2026-09-29 16:02:54</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-27 22:42:01</t>
+          <t>2026-09-29 16:22:54</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 22:52:01</t>
+          <t>2026-09-29 16:32:54</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-09-27 23:07:01</t>
+          <t>2026-09-29 16:47:54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1204,22 +1204,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-28 15:22:01</t>
+          <t>2026-09-30 09:02:54</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-28 17:22:01</t>
+          <t>2026-09-30 11:02:54</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28 17:52:01</t>
+          <t>2026-09-30 11:32:54</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-10-09 21:22:01</t>
+          <t>2026-10-11 15:02:54</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-29 15:22:01</t>
+          <t>2026-10-01 09:02:54</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-29 16:22:01</t>
+          <t>2026-10-01 10:02:54</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-29 16:52:01</t>
+          <t>2026-10-01 10:32:54</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:22:01</t>
+          <t>2026-10-01 17:02:54</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1470,22 +1470,22 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-29 18:22:01</t>
+          <t>2026-10-01 12:02:54</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-29 18:37:01</t>
+          <t>2026-10-01 12:17:54</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-29 18:52:01</t>
+          <t>2026-10-01 12:32:54</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-09-29 20:52:01</t>
+          <t>2026-10-01 14:32:54</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1601,22 +1601,22 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-30 15:22:01</t>
+          <t>2026-10-02 09:02:54</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-30 19:22:01</t>
+          <t>2026-10-02 13:02:54</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-30 21:22:01</t>
+          <t>2026-10-02 15:02:54</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-10-05 23:22:01</t>
+          <t>2026-10-07 17:02:54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-01 13:22:01</t>
+          <t>2026-10-03 07:02:54</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-10-01 15:22:01</t>
+          <t>2026-10-03 09:02:54</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-10-01 15:52:01</t>
+          <t>2026-10-03 09:32:54</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-10-01 17:22:01</t>
+          <t>2026-10-03 11:02:54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1863,22 +1863,22 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-02 16:22:01</t>
+          <t>2026-10-04 10:02:54</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-10-02 17:22:01</t>
+          <t>2026-10-04 11:02:54</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-10-02 17:52:01</t>
+          <t>2026-10-04 11:32:54</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:22:01</t>
+          <t>2026-10-08 13:02:54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1986,22 +1986,22 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-03 14:22:01</t>
+          <t>2026-10-05 08:02:54</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-10-03 14:22:01</t>
+          <t>2026-10-05 08:02:54</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-10-03 14:52:01</t>
+          <t>2026-10-05 08:32:54</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-10-03 15:52:01</t>
+          <t>2026-10-05 09:32:54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2117,22 +2117,22 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-04 17:22:01</t>
+          <t>2026-10-06 11:02:54</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-10-04 18:22:01</t>
+          <t>2026-10-06 12:02:54</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-10-04 18:52:01</t>
+          <t>2026-10-06 12:32:54</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-10-04 20:22:01</t>
+          <t>2026-10-06 14:02:54</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2248,22 +2248,22 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-05 16:22:01</t>
+          <t>2026-10-07 10:02:54</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-10-05 17:22:01</t>
+          <t>2026-10-07 11:02:54</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-10-05 17:37:01</t>
+          <t>2026-10-07 11:17:54</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-10-05 18:07:01</t>
+          <t>2026-10-07 11:47:54</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2379,22 +2379,22 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:01</t>
+          <t>2026-10-08 09:02:54</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-10-06 16:22:01</t>
+          <t>2026-10-08 10:02:54</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-10-06 16:52:01</t>
+          <t>2026-10-08 10:32:54</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-10-06 18:22:01</t>
+          <t>2026-10-08 12:02:54</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2510,22 +2510,22 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-07 21:22:01</t>
+          <t>2026-10-09 15:02:54</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-10-07 22:22:01</t>
+          <t>2026-10-09 16:02:54</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-10-07 22:52:01</t>
+          <t>2026-10-09 16:32:54</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-10-07 23:22:01</t>
+          <t>2026-10-09 17:02:54</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
